--- a/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
@@ -92,38 +92,22 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -137,18 +121,6 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">The command could not be loaded, possibly because:
-  * You intended to execute a .NET application:
-      The application '/apps/Server/Project11.dll' does not exist.
-  * You intended to execute a .NET SDK command:
-      No .NET SDKs were found.
-Download a .NET SDK:
-https://aka.ms/dotnet/download
-Learn about SDK resolution:
-https://aka.ms/dotnet/sdk-not-found
-</x:t>
-  </x:si>
-  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -209,6 +181,9 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -227,41 +202,10 @@
     <x:t>Data transfer in progress</x:t>
   </x:si>
   <x:si>
-    <x:t>ACK, PSH</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1 + 2
-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, RST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, FIN</x:t>
+    <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -288,7 +232,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -297,22 +241,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -335,7 +264,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -345,17 +274,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -369,18 +289,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -814,13 +722,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -911,7 +819,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -922,13 +830,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -940,10 +848,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -981,7 +889,7 @@
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="56.424911" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1040,7 +948,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -1048,16 +956,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -1069,7 +977,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -1080,16 +988,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -1101,10 +1009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1137,11 +1045,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P12"/>
+  <x:dimension ref="A1:P10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1151,7 +1059,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1163,49 +1071,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1216,7 +1124,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1225,31 +1133,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1266,40 +1174,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1316,7 +1224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1325,31 +1233,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1366,7 +1274,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1375,37 +1283,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O5" s="2" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="P5" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P5" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
@@ -1416,7 +1324,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1425,37 +1333,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="4" t="s">
-        <x:v>67</x:v>
+      <x:c r="P6" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1466,7 +1374,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1475,22 +1383,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1504,8 +1412,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="5" t="s">
-        <x:v>29</x:v>
+      <x:c r="P7" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1516,7 +1424,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1525,37 +1433,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>67</x:v>
+      <x:c r="P8" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1566,7 +1474,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1575,22 +1483,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
         <x:v>17</x:v>
@@ -1604,8 +1512,8 @@
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="5" t="s">
-        <x:v>29</x:v>
+      <x:c r="P9" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1616,7 +1524,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1625,22 +1533,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
         <x:v>17</x:v>
@@ -1654,108 +1562,8 @@
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="5" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:16">
-      <x:c r="A11" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="6" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:16">
-      <x:c r="A12" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="6" t="s">
-        <x:v>75</x:v>
+      <x:c r="P10" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
@@ -137,15 +137,10 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">The command could not be loaded, possibly because:
-  * You intended to execute a .NET application:
-      The application '/apps/Server/Project11.dll' does not exist.
-  * You intended to execute a .NET SDK command:
-      No .NET SDKs were found.
-Download a .NET SDK:
-https://aka.ms/dotnet/download
-Learn about SDK resolution:
-https://aka.ms/dotnet/sdk-not-found
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Waiting for a connection from client
 </x:t>
   </x:si>
   <x:si>
@@ -975,13 +970,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="56.424911" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1083,13 +1078,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -1101,10 +1096,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="S3" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1163,49 +1158,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1216,7 +1211,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1225,31 +1220,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
+      <x:c r="L2" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
+      <x:c r="M2" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1266,7 +1261,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1275,31 +1270,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="J3" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
+      <x:c r="L3" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1316,7 +1311,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1325,31 +1320,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
+      <x:c r="L4" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1366,7 +1361,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1375,34 +1370,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O5" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1416,7 +1411,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1425,31 +1420,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
@@ -1466,7 +1461,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1475,22 +1470,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1516,7 +1511,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1525,37 +1520,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1566,7 +1561,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1575,22 +1570,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
         <x:v>17</x:v>
@@ -1616,7 +1611,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1625,22 +1620,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
         <x:v>17</x:v>
@@ -1663,7 +1658,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>17</x:v>
@@ -1690,22 +1685,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="6" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:16">
@@ -1713,7 +1708,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>17</x:v>
@@ -1740,22 +1735,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="6" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="6" t="s">
-        <x:v>75</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
@@ -1635,22 +1635,22 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P10" s="5" t="s">
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:16">

--- a/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
@@ -229,31 +229,31 @@
 </x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACK, FIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARTIAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
     <x:t>ACK, RST</x:t>
   </x:si>
   <x:si>
     <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, FIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
   <x:si>
     <x:t>RST</x:t>
@@ -1132,7 +1132,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P12"/>
+  <x:dimension ref="A1:P13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -1438,19 +1438,19 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P6" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1485,7 +1485,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1535,22 +1535,22 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="5" t="s">
-        <x:v>73</x:v>
+      <x:c r="P8" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1570,10 +1570,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
@@ -1585,22 +1585,22 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P9" s="5" t="s">
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1635,22 +1635,22 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="5" t="s">
-        <x:v>73</x:v>
+      <x:c r="P10" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:16">
@@ -1658,7 +1658,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>17</x:v>
@@ -1700,7 +1700,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="6" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:16">
@@ -1708,37 +1708,37 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
         <x:v>59</x:v>
@@ -1750,7 +1750,57 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="6" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:16">
+      <x:c r="A13" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
         <x:v>76</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P13" s="6" t="s">
+        <x:v>74</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
@@ -92,38 +92,22 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -137,13 +121,6 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t>Text comparison passed: server output matches exactly</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Waiting for a connection from client
-</x:t>
-  </x:si>
-  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -204,6 +181,9 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -222,41 +202,10 @@
     <x:t>Data transfer in progress</x:t>
   </x:si>
   <x:si>
-    <x:t>ACK, PSH</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1 + 2
-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
     <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, FIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, RST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -283,7 +232,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -292,22 +241,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -330,7 +264,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -340,17 +274,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -364,18 +289,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -809,13 +722,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -906,7 +819,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -917,13 +830,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -935,10 +848,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -970,13 +883,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1035,7 +948,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -1043,16 +956,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -1064,7 +977,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -1075,7 +988,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1096,10 +1009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1132,11 +1045,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P13"/>
+  <x:dimension ref="A1:P10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1146,7 +1059,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1158,49 +1071,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1211,7 +1124,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1220,31 +1133,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1261,40 +1174,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1311,7 +1224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1320,31 +1233,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1361,7 +1274,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1370,34 +1283,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="O5" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1411,7 +1324,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1420,22 +1333,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1449,8 +1362,8 @@
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P6" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1461,7 +1374,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1470,22 +1383,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1499,8 +1412,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P7" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1511,7 +1424,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1520,22 +1433,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1549,8 +1462,8 @@
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P8" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1561,7 +1474,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1570,37 +1483,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="5" t="s">
-        <x:v>72</x:v>
+      <x:c r="P9" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1611,7 +1524,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1620,22 +1533,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
         <x:v>17</x:v>
@@ -1649,158 +1562,8 @@
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:16">
-      <x:c r="A11" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="6" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:16">
-      <x:c r="A12" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="6" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:16">
-      <x:c r="A13" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="M13" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P13" s="6" t="s">
-        <x:v>74</x:v>
+      <x:c r="P10" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
@@ -92,22 +92,38 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NONE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison passed: client output matches exactly</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+Enter operation (format as A X B):</x:t>
+  </x:si>
+  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -121,6 +137,13 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Waiting for a connection from client
+</x:t>
+  </x:si>
+  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -181,31 +204,53 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>SYN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server responding (SYN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection established</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSH, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data transfer in progress</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1 + 2
+</x:t>
+  </x:si>
+  <x:si>
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server responding (SYN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection established</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSH, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Data transfer in progress</x:t>
-  </x:si>
-  <x:si>
     <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARTIAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection reset (RST) - Error occurred</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -232,7 +277,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -241,7 +286,22 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF00"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -264,7 +324,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -274,8 +334,17 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -289,6 +358,18 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -722,13 +803,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -819,7 +900,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -830,13 +911,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -848,10 +929,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -883,13 +964,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -948,7 +1029,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -956,16 +1037,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -977,7 +1058,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -988,7 +1069,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1009,10 +1090,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1045,11 +1126,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P10"/>
+  <x:dimension ref="A1:P13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1059,7 +1140,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1071,49 +1152,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1124,7 +1205,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1133,31 +1214,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1174,7 +1255,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1183,31 +1264,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1224,7 +1305,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1233,31 +1314,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1274,7 +1355,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1283,34 +1364,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
+      <x:c r="J5" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="O5" s="2" t="s">
+        <x:v>66</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1324,7 +1405,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1333,22 +1414,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1362,8 +1443,8 @@
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P6" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1374,7 +1455,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1383,22 +1464,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1412,8 +1493,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P7" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1424,7 +1505,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1433,22 +1514,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1462,8 +1543,8 @@
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P8" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1474,7 +1555,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1483,37 +1564,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P9" s="5" t="s">
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1524,7 +1605,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1533,37 +1614,187 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P10" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:16">
+      <x:c r="A11" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G10" s="0" t="s">
+      <x:c r="L11" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P10" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="M11" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="6" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:16">
+      <x:c r="A12" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="6" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:16">
+      <x:c r="A13" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P13" s="6" t="s">
+        <x:v>72</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
@@ -92,38 +92,22 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -137,13 +121,6 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t>Text comparison passed: server output matches exactly</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Waiting for a connection from client
-</x:t>
-  </x:si>
-  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -204,6 +181,9 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -222,35 +202,10 @@
     <x:t>Data transfer in progress</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">1 + 2
-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
     <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -277,7 +232,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -286,22 +241,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -324,7 +264,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -334,17 +274,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -358,18 +289,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -803,13 +722,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -900,7 +819,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -911,13 +830,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -929,10 +848,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -964,13 +883,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1029,7 +948,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -1037,16 +956,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -1058,7 +977,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -1069,7 +988,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1090,10 +1009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1126,11 +1045,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P13"/>
+  <x:dimension ref="A1:P10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1140,7 +1059,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1152,49 +1071,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1205,7 +1124,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1214,31 +1133,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1255,40 +1174,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1305,7 +1224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1314,31 +1233,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1355,7 +1274,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1364,34 +1283,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="O5" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1405,7 +1324,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1414,22 +1333,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1443,8 +1362,8 @@
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P6" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1455,7 +1374,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1464,22 +1383,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1493,8 +1412,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P7" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1505,7 +1424,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1514,22 +1433,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1543,8 +1462,8 @@
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P8" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1555,7 +1474,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1564,37 +1483,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="5" t="s">
-        <x:v>70</x:v>
+      <x:c r="P9" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1605,7 +1524,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1614,22 +1533,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
         <x:v>17</x:v>
@@ -1643,158 +1562,8 @@
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:16">
-      <x:c r="A11" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="6" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:16">
-      <x:c r="A12" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="6" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:16">
-      <x:c r="A13" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="M13" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P13" s="6" t="s">
-        <x:v>72</x:v>
+      <x:c r="P10" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/hoangbsthe186345/TC4_Full/GradeDetail.xlsx
@@ -108,22 +108,6 @@
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -131,13 +115,15 @@
 Client disconnected</x:t>
   </x:si>
   <x:si>
-    <x:t>Text comparison failed: server output mismatch</x:t>
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Client connected
+Client disconnected
+</x:t>
   </x:si>
   <x:si>
     <x:t>Waiting for a connection from client</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: server output matches exactly</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Waiting for a connection from client
@@ -226,7 +212,7 @@
 </x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
+    <x:t>PARTIAL</x:t>
   </x:si>
   <x:si>
     <x:t>FIN, ACK</x:t>
@@ -235,22 +221,13 @@
     <x:t>Closing connection (FIN-ACK)</x:t>
   </x:si>
   <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
     <x:t>(Not validated by this test case)</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>RST, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
+    <x:t>3</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -277,7 +254,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -287,11 +264,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -324,7 +296,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -340,11 +312,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -366,10 +335,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -797,8 +762,8 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
@@ -911,13 +876,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -929,10 +894,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -958,8 +923,8 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
@@ -1029,7 +994,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -1037,16 +1002,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -1058,10 +1023,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S2" s="2" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -1069,7 +1034,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1090,10 +1055,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="S3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1126,7 +1091,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P13"/>
+  <x:dimension ref="A1:P19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -1139,8 +1104,8 @@
     <x:col min="8" max="8" width="4.996339" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1152,49 +1117,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="H1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="K1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1205,7 +1170,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1214,31 +1179,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1255,40 +1220,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1305,7 +1270,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1314,31 +1279,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1355,7 +1320,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1364,34 +1329,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O5" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1405,7 +1370,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1414,37 +1379,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P6" s="4" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P6" s="4" t="s">
-        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1455,7 +1420,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1464,37 +1429,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O7" s="2" t="s">
+        <x:v>61</x:v>
       </x:c>
       <x:c r="P7" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1505,7 +1470,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1514,37 +1479,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P8" s="4" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1555,7 +1520,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1564,37 +1529,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="5" t="s">
-        <x:v>70</x:v>
+      <x:c r="P9" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1605,7 +1570,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1614,37 +1579,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P10" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:16">
@@ -1652,7 +1617,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>17</x:v>
@@ -1679,22 +1644,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P11" s="6" t="s">
-        <x:v>72</x:v>
+      <x:c r="P11" s="5" t="s">
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:16">
@@ -1702,7 +1667,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>17</x:v>
@@ -1729,22 +1694,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P12" s="6" t="s">
-        <x:v>72</x:v>
+      <x:c r="P12" s="5" t="s">
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:16">
@@ -1752,7 +1717,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>17</x:v>
@@ -1779,22 +1744,322 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M13" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="P13" s="5" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:16">
+      <x:c r="A14" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P14" s="5" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:16">
+      <x:c r="A15" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="N13" s="0" t="s">
+      <x:c r="L15" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M15" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N15" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O15" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="P15" s="5" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:16">
+      <x:c r="A16" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K16" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L16" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="O13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P13" s="6" t="s">
-        <x:v>72</x:v>
+      <x:c r="M16" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N16" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P16" s="5" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:16">
+      <x:c r="A17" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="L17" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="M17" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N17" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P17" s="5" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:16">
+      <x:c r="A18" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K18" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M18" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N18" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P18" s="5" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:16">
+      <x:c r="A19" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K19" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L19" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M19" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N19" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P19" s="5" t="s">
+        <x:v>66</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
